--- a/INSTANCES/instances_WCTR_xlsx/A_MTN_8/231FL_10A.xlsx
+++ b/INSTANCES/instances_WCTR_xlsx/A_MTN_8/231FL_10A.xlsx
@@ -7806,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
